--- a/skills/qa/site-emissions-qa/Site_Emissions_QA_Template.xlsx
+++ b/skills/qa/site-emissions-qa/Site_Emissions_QA_Template.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Site Emissions QA" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mangrove Routing" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -46,8 +47,30 @@
       <color rgb="001F4E79"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F2D3D"/>
+    </font>
+    <font>
+      <color rgb="00833C00"/>
+    </font>
+    <font>
+      <color rgb="00276221"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00276221"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00833C00"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -64,8 +87,18 @@
         <fgColor rgb="00D6E4F0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDDCB5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -79,11 +112,25 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -100,6 +147,20 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2507,4 +2568,5098 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H168"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="56" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="inlineStr">
+        <is>
+          <t>Section Name</t>
+        </is>
+      </c>
+      <c r="C1" s="10" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="D1" s="10" t="inlineStr">
+        <is>
+          <t>Routing</t>
+        </is>
+      </c>
+      <c r="E1" s="10" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="F1" s="10" t="inlineStr">
+        <is>
+          <t>Automation / Review Notes</t>
+        </is>
+      </c>
+      <c r="H1" s="11" t="inlineStr">
+        <is>
+          <t>Mangrove Rules</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" s="12" t="inlineStr">
+        <is>
+          <t>Diesel</t>
+        </is>
+      </c>
+      <c r="C2" s="12" t="n"/>
+      <c r="D2" s="12" t="n"/>
+      <c r="E2" s="12" t="n"/>
+      <c r="F2" s="12" t="n"/>
+      <c r="H2" s="11" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>Diesel</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>All receipts accounted for in Diesel subfolder</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
+        <is>
+          <t>Charm Review</t>
+        </is>
+      </c>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>Document inventory</t>
+        </is>
+      </c>
+      <c r="F3" s="13" t="inlineStr">
+        <is>
+          <t>Cross-check file list against purchase records; count receipts = count deliveries</t>
+        </is>
+      </c>
+      <c r="H3" s="14" t="inlineStr">
+        <is>
+          <t>Charm Review Items</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="42" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>Diesel</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>All receipts entered in calc sheet</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>Charm Review</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>Document reading</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>Requires reading calc sheet rows against receipt dates and volumes</t>
+        </is>
+      </c>
+      <c r="H4" s="14" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" ht="42" customHeight="1">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>Diesel</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>Math correct in calc sheet (volume → mass conversion, EF application)</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="inlineStr">
+        <is>
+          <t>Arithmetic</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="inlineStr">
+        <is>
+          <t>volume × density_EF × emission_EF = emissions; check each step</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="42" customHeight="1">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>Diesel</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>EF matches Standard Emission Factors list for current year</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>Lookup / reference</t>
+        </is>
+      </c>
+      <c r="F6" s="15" t="inlineStr">
+        <is>
+          <t>EF = lookup(fuel='diesel', year=current); auto-fail on mismatch</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>Diesel</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>Diesel delivery transport distance and mass correct</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>Lookup + data field</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>distance = route_lookup; mass = invoice value; check both inputs</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="42" customHeight="1">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>Diesel</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>Diesel delivery transport process emissions correct (BCU-eligible)</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>Arithmetic</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>process_emiss = mass × distance × process_EF</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>Diesel</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>Diesel delivery transport embodied emissions correct (NOT BCU-eligible)</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>Arithmetic</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="inlineStr">
+        <is>
+          <t>embodied_emiss = distance × embodied_EF (round-trip for Charm truck delivery)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>Diesel</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>Certify diesel component matches calc sheet output</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>Cross-system match</t>
+        </is>
+      </c>
+      <c r="F10" s="15" t="inlineStr">
+        <is>
+          <t>certify_diesel = calc_diesel; tolerance ±0.001 tCO2e</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>Diesel</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>BCU applied to eligible components only (consumption + delivery process)</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>Eligibility rule</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="inlineStr">
+        <is>
+          <t>BCU eligible = consumption + delivery_process; delivery embodied is NOT eligible</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>Gasoline</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="n"/>
+      <c r="D12" s="12" t="n"/>
+      <c r="E12" s="12" t="n"/>
+      <c r="F12" s="12" t="n"/>
+    </row>
+    <row r="13" ht="42" customHeight="1">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>Gasoline</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>All receipts in Gasoline subfolder</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>Charm Review</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>Document inventory</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>Cross-check file list against purchase records</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="42" customHeight="1">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>Gasoline</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>All receipts entered in calc sheet</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>Charm Review</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>Document reading</t>
+        </is>
+      </c>
+      <c r="F14" s="13" t="inlineStr">
+        <is>
+          <t>Requires reading calc sheet against receipt dates</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="42" customHeight="1">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>Gasoline</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>Math correct in calc sheet</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E15" s="15" t="inlineStr">
+        <is>
+          <t>Arithmetic</t>
+        </is>
+      </c>
+      <c r="F15" s="15" t="inlineStr">
+        <is>
+          <t>volume × density × EF = emissions</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="42" customHeight="1">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>Gasoline</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>EF matches Standard Emission Factors list</t>
+        </is>
+      </c>
+      <c r="D16" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E16" s="15" t="inlineStr">
+        <is>
+          <t>Lookup / reference</t>
+        </is>
+      </c>
+      <c r="F16" s="15" t="inlineStr">
+        <is>
+          <t>EF = lookup(fuel='gasoline', year=current)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="42" customHeight="1">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>Gasoline</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>No transport emissions included (gasoline is self-delivered)</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E17" s="15" t="inlineStr">
+        <is>
+          <t>Absence check</t>
+        </is>
+      </c>
+      <c r="F17" s="15" t="inlineStr">
+        <is>
+          <t>transport_emissions[gasoline] = 0; any non-zero = fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>Gasoline</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>No BCU offset applied (gasoline NEVER BCU-eligible)</t>
+        </is>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E18" s="15" t="inlineStr">
+        <is>
+          <t>Absence check</t>
+        </is>
+      </c>
+      <c r="F18" s="15" t="inlineStr">
+        <is>
+          <t>BCU[gasoline] = 0; any non-zero = fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>Gasoline</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>Certify gasoline component matches calc sheet</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E19" s="15" t="inlineStr">
+        <is>
+          <t>Cross-system match</t>
+        </is>
+      </c>
+      <c r="F19" s="15" t="inlineStr">
+        <is>
+          <t>certify_gasoline = calc_gasoline</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>Methanol</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="n"/>
+      <c r="D20" s="12" t="n"/>
+      <c r="E20" s="12" t="n"/>
+      <c r="F20" s="12" t="n"/>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>Methanol</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>All receipts in Methanol subfolder</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>Charm Review</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>Document inventory</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="inlineStr">
+        <is>
+          <t>Cross-check file list against purchase records</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>Methanol</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>All receipts entered in calc sheet</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>Charm Review</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>Document reading</t>
+        </is>
+      </c>
+      <c r="F22" s="13" t="inlineStr">
+        <is>
+          <t>Requires reading calc sheet against receipt dates</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>Methanol</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>Math correct (consumption + transport)</t>
+        </is>
+      </c>
+      <c r="D23" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E23" s="15" t="inlineStr">
+        <is>
+          <t>Arithmetic</t>
+        </is>
+      </c>
+      <c r="F23" s="15" t="inlineStr">
+        <is>
+          <t>consumption_emiss + transport_proc + transport_emb = total</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>Methanol</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>Transport distance correct and documented</t>
+        </is>
+      </c>
+      <c r="D24" s="13" t="inlineStr">
+        <is>
+          <t>Charm Review</t>
+        </is>
+      </c>
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <t>Evidence linking</t>
+        </is>
+      </c>
+      <c r="F24" s="13" t="inlineStr">
+        <is>
+          <t>Requires confirming route documentation is attached</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
+          <t>Methanol</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>Transport mass correct (matches purchase records)</t>
+        </is>
+      </c>
+      <c r="D25" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E25" s="15" t="inlineStr">
+        <is>
+          <t>Cross-field match</t>
+        </is>
+      </c>
+      <c r="F25" s="15" t="inlineStr">
+        <is>
+          <t>transport_mass = invoiced_mass from purchase records</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="inlineStr">
+        <is>
+          <t>Methanol</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="inlineStr">
+        <is>
+          <t>Transport process emissions correct (BCU-eligible)</t>
+        </is>
+      </c>
+      <c r="D26" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E26" s="15" t="inlineStr">
+        <is>
+          <t>Arithmetic</t>
+        </is>
+      </c>
+      <c r="F26" s="15" t="inlineStr">
+        <is>
+          <t>process_emiss = mass × distance × process_EF</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>Methanol</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="inlineStr">
+        <is>
+          <t>Transport embodied/consumption correct (NOT BCU-eligible)</t>
+        </is>
+      </c>
+      <c r="D27" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E27" s="15" t="inlineStr">
+        <is>
+          <t>Arithmetic</t>
+        </is>
+      </c>
+      <c r="F27" s="15" t="inlineStr">
+        <is>
+          <t>embodied = distance × embodied_EF</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t>Methanol</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="inlineStr">
+        <is>
+          <t>EF matches Standard Emission Factors list</t>
+        </is>
+      </c>
+      <c r="D28" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E28" s="15" t="inlineStr">
+        <is>
+          <t>Lookup / reference</t>
+        </is>
+      </c>
+      <c r="F28" s="15" t="inlineStr">
+        <is>
+          <t>EF = lookup(fuel='methanol', year=current)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="inlineStr">
+        <is>
+          <t>Methanol</t>
+        </is>
+      </c>
+      <c r="C29" s="15" t="inlineStr">
+        <is>
+          <t>Certify methanol matches calc total</t>
+        </is>
+      </c>
+      <c r="D29" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E29" s="15" t="inlineStr">
+        <is>
+          <t>Cross-system match</t>
+        </is>
+      </c>
+      <c r="F29" s="15" t="inlineStr">
+        <is>
+          <t>certify_methanol = calc_total</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>Argon</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="n"/>
+      <c r="D30" s="12" t="n"/>
+      <c r="E30" s="12" t="n"/>
+      <c r="F30" s="12" t="n"/>
+    </row>
+    <row r="31" ht="42" customHeight="1">
+      <c r="A31" s="13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>Argon</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="inlineStr">
+        <is>
+          <t>All receipts in Argon subfolder (cylinder rentals excluded)</t>
+        </is>
+      </c>
+      <c r="D31" s="13" t="inlineStr">
+        <is>
+          <t>Charm Review</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>Document inventory</t>
+        </is>
+      </c>
+      <c r="F31" s="13" t="inlineStr">
+        <is>
+          <t>Confirm purchase receipts only; rental invoices explicitly excluded</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="42" customHeight="1">
+      <c r="A32" s="13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>Argon</t>
+        </is>
+      </c>
+      <c r="C32" s="13" t="inlineStr">
+        <is>
+          <t>All receipts entered in calc sheet</t>
+        </is>
+      </c>
+      <c r="D32" s="13" t="inlineStr">
+        <is>
+          <t>Charm Review</t>
+        </is>
+      </c>
+      <c r="E32" s="13" t="inlineStr">
+        <is>
+          <t>Document reading</t>
+        </is>
+      </c>
+      <c r="F32" s="13" t="inlineStr">
+        <is>
+          <t>Requires reading calc sheet against receipt dates</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="42" customHeight="1">
+      <c r="A33" s="15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B33" s="15" t="inlineStr">
+        <is>
+          <t>Argon</t>
+        </is>
+      </c>
+      <c r="C33" s="15" t="inlineStr">
+        <is>
+          <t>Math correct in argon calc sheet</t>
+        </is>
+      </c>
+      <c r="D33" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E33" s="15" t="inlineStr">
+        <is>
+          <t>Arithmetic</t>
+        </is>
+      </c>
+      <c r="F33" s="15" t="inlineStr">
+        <is>
+          <t>Check all steps: mass, transport, electricity sub-calcs</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="42" customHeight="1">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>Argon</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="inlineStr">
+        <is>
+          <t>Transport distance correct and documented</t>
+        </is>
+      </c>
+      <c r="D34" s="13" t="inlineStr">
+        <is>
+          <t>Charm Review</t>
+        </is>
+      </c>
+      <c r="E34" s="13" t="inlineStr">
+        <is>
+          <t>Evidence linking</t>
+        </is>
+      </c>
+      <c r="F34" s="13" t="inlineStr">
+        <is>
+          <t>Requires confirming route documentation is attached</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="42" customHeight="1">
+      <c r="A35" s="15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B35" s="15" t="inlineStr">
+        <is>
+          <t>Argon</t>
+        </is>
+      </c>
+      <c r="C35" s="15" t="inlineStr">
+        <is>
+          <t>Transport mass correct</t>
+        </is>
+      </c>
+      <c r="D35" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E35" s="15" t="inlineStr">
+        <is>
+          <t>Cross-field match</t>
+        </is>
+      </c>
+      <c r="F35" s="15" t="inlineStr">
+        <is>
+          <t>transport_mass = invoiced_mass</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="42" customHeight="1">
+      <c r="A36" s="15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B36" s="15" t="inlineStr">
+        <is>
+          <t>Argon</t>
+        </is>
+      </c>
+      <c r="C36" s="15" t="inlineStr">
+        <is>
+          <t>Transport process emissions correct (BCU-eligible)</t>
+        </is>
+      </c>
+      <c r="D36" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E36" s="15" t="inlineStr">
+        <is>
+          <t>Arithmetic</t>
+        </is>
+      </c>
+      <c r="F36" s="15" t="inlineStr">
+        <is>
+          <t>process_emiss = mass × distance × process_EF</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="42" customHeight="1">
+      <c r="A37" s="15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B37" s="15" t="inlineStr">
+        <is>
+          <t>Argon</t>
+        </is>
+      </c>
+      <c r="C37" s="15" t="inlineStr">
+        <is>
+          <t>Transport embodied emissions correct (NOT BCU-eligible)</t>
+        </is>
+      </c>
+      <c r="D37" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E37" s="15" t="inlineStr">
+        <is>
+          <t>Arithmetic</t>
+        </is>
+      </c>
+      <c r="F37" s="15" t="inlineStr">
+        <is>
+          <t>embodied_emiss = distance × embodied_EF</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="42" customHeight="1">
+      <c r="A38" s="15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B38" s="15" t="inlineStr">
+        <is>
+          <t>Argon</t>
+        </is>
+      </c>
+      <c r="C38" s="15" t="inlineStr">
+        <is>
+          <t>Argon electricity usage correctly calculated (sole emissive input; REC-eligible)</t>
+        </is>
+      </c>
+      <c r="D38" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E38" s="15" t="inlineStr">
+        <is>
+          <t>Arithmetic</t>
+        </is>
+      </c>
+      <c r="F38" s="15" t="inlineStr">
+        <is>
+          <t>electricity_emiss = kWh × grid_EF; REC substitution applied separately</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="42" customHeight="1">
+      <c r="A39" s="15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B39" s="15" t="inlineStr">
+        <is>
+          <t>Argon</t>
+        </is>
+      </c>
+      <c r="C39" s="15" t="inlineStr">
+        <is>
+          <t>EFs match Standard Emission Factors list</t>
+        </is>
+      </c>
+      <c r="D39" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E39" s="15" t="inlineStr">
+        <is>
+          <t>Lookup / reference</t>
+        </is>
+      </c>
+      <c r="F39" s="15" t="inlineStr">
+        <is>
+          <t>EF = lookup(input='argon', year=current) for all sub-components</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="42" customHeight="1">
+      <c r="A40" s="15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B40" s="15" t="inlineStr">
+        <is>
+          <t>Argon</t>
+        </is>
+      </c>
+      <c r="C40" s="15" t="inlineStr">
+        <is>
+          <t>Certify argon component values match calc outputs (all sub-components)</t>
+        </is>
+      </c>
+      <c r="D40" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E40" s="15" t="inlineStr">
+        <is>
+          <t>Cross-system match</t>
+        </is>
+      </c>
+      <c r="F40" s="15" t="inlineStr">
+        <is>
+          <t>certify_argon = calc_argon for each sub-component</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>Electricity</t>
+        </is>
+      </c>
+      <c r="C41" s="12" t="n"/>
+      <c r="D41" s="12" t="n"/>
+      <c r="E41" s="12" t="n"/>
+      <c r="F41" s="12" t="n"/>
+    </row>
+    <row r="42" ht="42" customHeight="1">
+      <c r="A42" s="15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B42" s="15" t="inlineStr">
+        <is>
+          <t>Electricity</t>
+        </is>
+      </c>
+      <c r="C42" s="15" t="inlineStr">
+        <is>
+          <t>Utility readout dates cover all RP dates</t>
+        </is>
+      </c>
+      <c r="D42" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E42" s="15" t="inlineStr">
+        <is>
+          <t>Date range check</t>
+        </is>
+      </c>
+      <c r="F42" s="15" t="inlineStr">
+        <is>
+          <t>date_range(utility_readout) ⊇ date_range(RP); flag any gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="42" customHeight="1">
+      <c r="A43" s="13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B43" s="13" t="inlineStr">
+        <is>
+          <t>Electricity</t>
+        </is>
+      </c>
+      <c r="C43" s="13" t="inlineStr">
+        <is>
+          <t>Total kWh includes all dates in RP</t>
+        </is>
+      </c>
+      <c r="D43" s="13" t="inlineStr">
+        <is>
+          <t>Charm Review</t>
+        </is>
+      </c>
+      <c r="E43" s="13" t="inlineStr">
+        <is>
+          <t>Document reading</t>
+        </is>
+      </c>
+      <c r="F43" s="13" t="inlineStr">
+        <is>
+          <t>Requires reading utility readout to confirm full-period coverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="42" customHeight="1">
+      <c r="A44" s="15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B44" s="15" t="inlineStr">
+        <is>
+          <t>Electricity</t>
+        </is>
+      </c>
+      <c r="C44" s="15" t="inlineStr">
+        <is>
+          <t>Grid EF and REC generator EF correct (source documented)</t>
+        </is>
+      </c>
+      <c r="D44" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E44" s="15" t="inlineStr">
+        <is>
+          <t>Lookup / reference</t>
+        </is>
+      </c>
+      <c r="F44" s="15" t="inlineStr">
+        <is>
+          <t>EF = lookup(grid, year=current) and lookup(REC_generator, year=current)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="42" customHeight="1">
+      <c r="A45" s="15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B45" s="15" t="inlineStr">
+        <is>
+          <t>Electricity</t>
+        </is>
+      </c>
+      <c r="C45" s="15" t="inlineStr">
+        <is>
+          <t>REC kWh matches consumed electricity kWh (substitution, not subtraction)</t>
+        </is>
+      </c>
+      <c r="D45" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E45" s="15" t="inlineStr">
+        <is>
+          <t>Equality check</t>
+        </is>
+      </c>
+      <c r="F45" s="15" t="inlineStr">
+        <is>
+          <t>REC_kWh = consumed_kWh; method is substitution — verify formula structure</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="42" customHeight="1">
+      <c r="A46" s="15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B46" s="15" t="inlineStr">
+        <is>
+          <t>Electricity</t>
+        </is>
+      </c>
+      <c r="C46" s="15" t="inlineStr">
+        <is>
+          <t>Net electricity emissions correctly calculated</t>
+        </is>
+      </c>
+      <c r="D46" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E46" s="15" t="inlineStr">
+        <is>
+          <t>Arithmetic</t>
+        </is>
+      </c>
+      <c r="F46" s="15" t="inlineStr">
+        <is>
+          <t>net = (grid_kWh − REC_kWh) × grid_EF (or substitution method per protocol)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="42" customHeight="1">
+      <c r="A47" s="15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B47" s="15" t="inlineStr">
+        <is>
+          <t>Electricity</t>
+        </is>
+      </c>
+      <c r="C47" s="15" t="inlineStr">
+        <is>
+          <t>No double-counting with argon electricity</t>
+        </is>
+      </c>
+      <c r="D47" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E47" s="15" t="inlineStr">
+        <is>
+          <t>Exclusion check</t>
+        </is>
+      </c>
+      <c r="F47" s="15" t="inlineStr">
+        <is>
+          <t>electricity_sub excludes kWh already counted under argon; verify no overlap</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="42" customHeight="1">
+      <c r="A48" s="15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B48" s="15" t="inlineStr">
+        <is>
+          <t>Electricity</t>
+        </is>
+      </c>
+      <c r="C48" s="15" t="inlineStr">
+        <is>
+          <t>Certify electricity matches calc output</t>
+        </is>
+      </c>
+      <c r="D48" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E48" s="15" t="inlineStr">
+        <is>
+          <t>Cross-system match</t>
+        </is>
+      </c>
+      <c r="F48" s="15" t="inlineStr">
+        <is>
+          <t>certify_electricity = calc_electricity</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="16" customHeight="1">
+      <c r="A49" s="12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B49" s="12" t="inlineStr">
+        <is>
+          <t>Brine (Flush Fluid)</t>
+        </is>
+      </c>
+      <c r="C49" s="12" t="n"/>
+      <c r="D49" s="12" t="n"/>
+      <c r="E49" s="12" t="n"/>
+      <c r="F49" s="12" t="n"/>
+    </row>
+    <row r="50" ht="42" customHeight="1">
+      <c r="A50" s="13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B50" s="13" t="inlineStr">
+        <is>
+          <t>Brine (Flush Fluid)</t>
+        </is>
+      </c>
+      <c r="C50" s="13" t="inlineStr">
+        <is>
+          <t>Brine volume sanity check (totalizer or invoices make sense given operations)</t>
+        </is>
+      </c>
+      <c r="D50" s="13" t="inlineStr">
+        <is>
+          <t>Charm Review</t>
+        </is>
+      </c>
+      <c r="E50" s="13" t="inlineStr">
+        <is>
+          <t>Judgment call</t>
+        </is>
+      </c>
+      <c r="F50" s="13" t="inlineStr">
+        <is>
+          <t>Requires human baseline knowledge of injection volumes to assess reasonableness</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="42" customHeight="1">
+      <c r="A51" s="13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B51" s="13" t="inlineStr">
+        <is>
+          <t>Brine (Flush Fluid)</t>
+        </is>
+      </c>
+      <c r="C51" s="13" t="inlineStr">
+        <is>
+          <t>All Borque invoices present (if invoice method used)</t>
+        </is>
+      </c>
+      <c r="D51" s="13" t="inlineStr">
+        <is>
+          <t>Charm Review</t>
+        </is>
+      </c>
+      <c r="E51" s="13" t="inlineStr">
+        <is>
+          <t>Document inventory</t>
+        </is>
+      </c>
+      <c r="F51" s="13" t="inlineStr">
+        <is>
+          <t>Cross-check file list against delivery records from Borque</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="42" customHeight="1">
+      <c r="A52" s="15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B52" s="15" t="inlineStr">
+        <is>
+          <t>Brine (Flush Fluid)</t>
+        </is>
+      </c>
+      <c r="C52" s="15" t="inlineStr">
+        <is>
+          <t>Total reflects sum of invoiced volumes</t>
+        </is>
+      </c>
+      <c r="D52" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E52" s="15" t="inlineStr">
+        <is>
+          <t>Arithmetic</t>
+        </is>
+      </c>
+      <c r="F52" s="15" t="inlineStr">
+        <is>
+          <t>Σ(invoice_volume_i) = total_brine_volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="42" customHeight="1">
+      <c r="A53" s="15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B53" s="15" t="inlineStr">
+        <is>
+          <t>Brine (Flush Fluid)</t>
+        </is>
+      </c>
+      <c r="C53" s="15" t="inlineStr">
+        <is>
+          <t>Average transport distance applied correctly (from Standard EF sheet)</t>
+        </is>
+      </c>
+      <c r="D53" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E53" s="15" t="inlineStr">
+        <is>
+          <t>Lookup / reference</t>
+        </is>
+      </c>
+      <c r="F53" s="15" t="inlineStr">
+        <is>
+          <t>distance = lookup(brine_route_average) from Standard EF list</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="42" customHeight="1">
+      <c r="A54" s="15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B54" s="15" t="inlineStr">
+        <is>
+          <t>Brine (Flush Fluid)</t>
+        </is>
+      </c>
+      <c r="C54" s="15" t="inlineStr">
+        <is>
+          <t>Per-gallon transport process emissions correct (BCU-eligible)</t>
+        </is>
+      </c>
+      <c r="D54" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E54" s="15" t="inlineStr">
+        <is>
+          <t>Arithmetic</t>
+        </is>
+      </c>
+      <c r="F54" s="15" t="inlineStr">
+        <is>
+          <t>process_emiss = volume × process_EF_per_gallon</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="42" customHeight="1">
+      <c r="A55" s="15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B55" s="15" t="inlineStr">
+        <is>
+          <t>Brine (Flush Fluid)</t>
+        </is>
+      </c>
+      <c r="C55" s="15" t="inlineStr">
+        <is>
+          <t>Per-gallon transport embodied emissions correct (NOT BCU-eligible)</t>
+        </is>
+      </c>
+      <c r="D55" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E55" s="15" t="inlineStr">
+        <is>
+          <t>Arithmetic</t>
+        </is>
+      </c>
+      <c r="F55" s="15" t="inlineStr">
+        <is>
+          <t>embodied_emiss = volume × embodied_EF_per_gallon</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="42" customHeight="1">
+      <c r="A56" s="15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B56" s="15" t="inlineStr">
+        <is>
+          <t>Brine (Flush Fluid)</t>
+        </is>
+      </c>
+      <c r="C56" s="15" t="inlineStr">
+        <is>
+          <t>Process and embodied computed as separate fields (required for BCU eligibility)</t>
+        </is>
+      </c>
+      <c r="D56" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E56" s="15" t="inlineStr">
+        <is>
+          <t>Field structure check</t>
+        </is>
+      </c>
+      <c r="F56" s="15" t="inlineStr">
+        <is>
+          <t>Two separate values in calc; combined single value = fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="42" customHeight="1">
+      <c r="A57" s="15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B57" s="15" t="inlineStr">
+        <is>
+          <t>Brine (Flush Fluid)</t>
+        </is>
+      </c>
+      <c r="C57" s="15" t="inlineStr">
+        <is>
+          <t>EFs match Standard Emission Factors list</t>
+        </is>
+      </c>
+      <c r="D57" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E57" s="15" t="inlineStr">
+        <is>
+          <t>Lookup / reference</t>
+        </is>
+      </c>
+      <c r="F57" s="15" t="inlineStr">
+        <is>
+          <t>EF = lookup(fluid='brine', year=current) for process and embodied</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="42" customHeight="1">
+      <c r="A58" s="15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B58" s="15" t="inlineStr">
+        <is>
+          <t>Brine (Flush Fluid)</t>
+        </is>
+      </c>
+      <c r="C58" s="15" t="inlineStr">
+        <is>
+          <t>Certify brine values match calc outputs (process + embodied)</t>
+        </is>
+      </c>
+      <c r="D58" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E58" s="15" t="inlineStr">
+        <is>
+          <t>Cross-system match</t>
+        </is>
+      </c>
+      <c r="F58" s="15" t="inlineStr">
+        <is>
+          <t>certify_brine_{proc,emb} = calc_brine_{proc,emb}</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="42" customHeight="1">
+      <c r="A59" s="15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B59" s="15" t="inlineStr">
+        <is>
+          <t>Brine (Flush Fluid)</t>
+        </is>
+      </c>
+      <c r="C59" s="15" t="inlineStr">
+        <is>
+          <t>BCU applied to process emissions only (not embodied)</t>
+        </is>
+      </c>
+      <c r="D59" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E59" s="15" t="inlineStr">
+        <is>
+          <t>Eligibility rule</t>
+        </is>
+      </c>
+      <c r="F59" s="15" t="inlineStr">
+        <is>
+          <t>BCU[brine_embodied] = 0; BCU[brine_process] may be non-zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="16" customHeight="1">
+      <c r="A60" s="12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B60" s="12" t="inlineStr">
+        <is>
+          <t>Support Travel</t>
+        </is>
+      </c>
+      <c r="C60" s="12" t="n"/>
+      <c r="D60" s="12" t="n"/>
+      <c r="E60" s="12" t="n"/>
+      <c r="F60" s="12" t="n"/>
+    </row>
+    <row r="61" ht="42" customHeight="1">
+      <c r="A61" s="13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B61" s="13" t="inlineStr">
+        <is>
+          <t>Support Travel</t>
+        </is>
+      </c>
+      <c r="C61" s="13" t="inlineStr">
+        <is>
+          <t>All RP trips included in calc sheet</t>
+        </is>
+      </c>
+      <c r="D61" s="13" t="inlineStr">
+        <is>
+          <t>Charm Review</t>
+        </is>
+      </c>
+      <c r="E61" s="13" t="inlineStr">
+        <is>
+          <t>Document reading</t>
+        </is>
+      </c>
+      <c r="F61" s="13" t="inlineStr">
+        <is>
+          <t>Requires reviewing travel records / trip approvals against calc sheet rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="42" customHeight="1">
+      <c r="A62" s="13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B62" s="13" t="inlineStr">
+        <is>
+          <t>Support Travel</t>
+        </is>
+      </c>
+      <c r="C62" s="13" t="inlineStr">
+        <is>
+          <t>Legs and distances correct per trip</t>
+        </is>
+      </c>
+      <c r="D62" s="13" t="inlineStr">
+        <is>
+          <t>Charm Review</t>
+        </is>
+      </c>
+      <c r="E62" s="13" t="inlineStr">
+        <is>
+          <t>Document reading</t>
+        </is>
+      </c>
+      <c r="F62" s="13" t="inlineStr">
+        <is>
+          <t>Requires reading itineraries and verifying distances in calc sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="42" customHeight="1">
+      <c r="A63" s="15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B63" s="15" t="inlineStr">
+        <is>
+          <t>Support Travel</t>
+        </is>
+      </c>
+      <c r="C63" s="15" t="inlineStr">
+        <is>
+          <t>Correct EF per transport mode per leg (SAF for air, gasoline for car)</t>
+        </is>
+      </c>
+      <c r="D63" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E63" s="15" t="inlineStr">
+        <is>
+          <t>Lookup / reference</t>
+        </is>
+      </c>
+      <c r="F63" s="15" t="inlineStr">
+        <is>
+          <t>EF = lookup(mode, year=current) per leg; wrong mode = fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="42" customHeight="1">
+      <c r="A64" s="15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B64" s="15" t="inlineStr">
+        <is>
+          <t>Support Travel</t>
+        </is>
+      </c>
+      <c r="C64" s="15" t="inlineStr">
+        <is>
+          <t>Correct sum of emissions for period</t>
+        </is>
+      </c>
+      <c r="D64" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E64" s="15" t="inlineStr">
+        <is>
+          <t>Arithmetic</t>
+        </is>
+      </c>
+      <c r="F64" s="15" t="inlineStr">
+        <is>
+          <t>total = Σ(leg_distance × leg_EF) across all trips</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="42" customHeight="1">
+      <c r="A65" s="13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B65" s="13" t="inlineStr">
+        <is>
+          <t>Support Travel</t>
+        </is>
+      </c>
+      <c r="C65" s="13" t="inlineStr">
+        <is>
+          <t>Distance evidence present for each route</t>
+        </is>
+      </c>
+      <c r="D65" s="13" t="inlineStr">
+        <is>
+          <t>Charm Review</t>
+        </is>
+      </c>
+      <c r="E65" s="13" t="inlineStr">
+        <is>
+          <t>Evidence linking</t>
+        </is>
+      </c>
+      <c r="F65" s="13" t="inlineStr">
+        <is>
+          <t>Requires confirming route docs (itinerary, booking) attached per trip</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="42" customHeight="1">
+      <c r="A66" s="15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B66" s="15" t="inlineStr">
+        <is>
+          <t>Support Travel</t>
+        </is>
+      </c>
+      <c r="C66" s="15" t="inlineStr">
+        <is>
+          <t>No BCU applied (SAF and gasoline NEVER BCU-eligible)</t>
+        </is>
+      </c>
+      <c r="D66" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E66" s="15" t="inlineStr">
+        <is>
+          <t>Absence check</t>
+        </is>
+      </c>
+      <c r="F66" s="15" t="inlineStr">
+        <is>
+          <t>BCU[travel] = 0; any non-zero = fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="42" customHeight="1">
+      <c r="A67" s="15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B67" s="15" t="inlineStr">
+        <is>
+          <t>Support Travel</t>
+        </is>
+      </c>
+      <c r="C67" s="15" t="inlineStr">
+        <is>
+          <t>Certify travel matches calc total</t>
+        </is>
+      </c>
+      <c r="D67" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E67" s="15" t="inlineStr">
+        <is>
+          <t>Cross-system match</t>
+        </is>
+      </c>
+      <c r="F67" s="15" t="inlineStr">
+        <is>
+          <t>certify_travel = calc_travel</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="16" customHeight="1">
+      <c r="A68" s="12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B68" s="12" t="inlineStr">
+        <is>
+          <t>Embodied — CapEx</t>
+        </is>
+      </c>
+      <c r="C68" s="12" t="n"/>
+      <c r="D68" s="12" t="n"/>
+      <c r="E68" s="12" t="n"/>
+      <c r="F68" s="12" t="n"/>
+    </row>
+    <row r="69" ht="42" customHeight="1">
+      <c r="A69" s="13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B69" s="13" t="inlineStr">
+        <is>
+          <t>Embodied — CapEx</t>
+        </is>
+      </c>
+      <c r="C69" s="13" t="inlineStr">
+        <is>
+          <t>CE Inventory fully updated for current operations</t>
+        </is>
+      </c>
+      <c r="D69" s="13" t="inlineStr">
+        <is>
+          <t>Charm Review</t>
+        </is>
+      </c>
+      <c r="E69" s="13" t="inlineStr">
+        <is>
+          <t>Judgment call</t>
+        </is>
+      </c>
+      <c r="F69" s="13" t="inlineStr">
+        <is>
+          <t>Requires reviewing inventory against known site assets; cannot be automated</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="42" customHeight="1">
+      <c r="A70" s="13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B70" s="13" t="inlineStr">
+        <is>
+          <t>Embodied — CapEx</t>
+        </is>
+      </c>
+      <c r="C70" s="13" t="inlineStr">
+        <is>
+          <t>LCA sheets completed for each inventory line item</t>
+        </is>
+      </c>
+      <c r="D70" s="13" t="inlineStr">
+        <is>
+          <t>Charm Review</t>
+        </is>
+      </c>
+      <c r="E70" s="13" t="inlineStr">
+        <is>
+          <t>Document inventory</t>
+        </is>
+      </c>
+      <c r="F70" s="13" t="inlineStr">
+        <is>
+          <t>Requires checking each line item has an LCA document linked</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="42" customHeight="1">
+      <c r="A71" s="15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B71" s="15" t="inlineStr">
+        <is>
+          <t>Embodied — CapEx</t>
+        </is>
+      </c>
+      <c r="C71" s="15" t="inlineStr">
+        <is>
+          <t>Line item GWP = LCA EF × unit count</t>
+        </is>
+      </c>
+      <c r="D71" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E71" s="15" t="inlineStr">
+        <is>
+          <t>Arithmetic</t>
+        </is>
+      </c>
+      <c r="F71" s="15" t="inlineStr">
+        <is>
+          <t>GWP_i = LCA_EF_i × unit_count_i; check each row</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="42" customHeight="1">
+      <c r="A72" s="15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B72" s="15" t="inlineStr">
+        <is>
+          <t>Embodied — CapEx</t>
+        </is>
+      </c>
+      <c r="C72" s="15" t="inlineStr">
+        <is>
+          <t>Amortization pool = sum of all current GWPs</t>
+        </is>
+      </c>
+      <c r="D72" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E72" s="15" t="inlineStr">
+        <is>
+          <t>Arithmetic</t>
+        </is>
+      </c>
+      <c r="F72" s="15" t="inlineStr">
+        <is>
+          <t>pool = Σ(GWP_i)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="42" customHeight="1">
+      <c r="A73" s="15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B73" s="15" t="inlineStr">
+        <is>
+          <t>Embodied — CapEx</t>
+        </is>
+      </c>
+      <c r="C73" s="15" t="inlineStr">
+        <is>
+          <t>Amortization factor computed using GROSS removals (not net)</t>
+        </is>
+      </c>
+      <c r="D73" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E73" s="15" t="inlineStr">
+        <is>
+          <t>Formula check</t>
+        </is>
+      </c>
+      <c r="F73" s="15" t="inlineStr">
+        <is>
+          <t>denominator = gross_removals; using net removals = fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="42" customHeight="1">
+      <c r="A74" s="15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B74" s="15" t="inlineStr">
+        <is>
+          <t>Embodied — CapEx</t>
+        </is>
+      </c>
+      <c r="C74" s="15" t="inlineStr">
+        <is>
+          <t>Emission penalty computed correctly</t>
+        </is>
+      </c>
+      <c r="D74" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E74" s="15" t="inlineStr">
+        <is>
+          <t>Arithmetic</t>
+        </is>
+      </c>
+      <c r="F74" s="15" t="inlineStr">
+        <is>
+          <t>penalty = pool × amortization_factor</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="42" customHeight="1">
+      <c r="A75" s="15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B75" s="15" t="inlineStr">
+        <is>
+          <t>Embodied — CapEx</t>
+        </is>
+      </c>
+      <c r="C75" s="15" t="inlineStr">
+        <is>
+          <t>New sitework: non-diesel remainder added to CapEx inventory for amortization</t>
+        </is>
+      </c>
+      <c r="D75" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E75" s="15" t="inlineStr">
+        <is>
+          <t>Conditional presence</t>
+        </is>
+      </c>
+      <c r="F75" s="15" t="inlineStr">
+        <is>
+          <t>IF new_sitework: non_diesel_GWP → capex_inventory; verify row added</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="42" customHeight="1">
+      <c r="A76" s="15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B76" s="15" t="inlineStr">
+        <is>
+          <t>Embodied — CapEx</t>
+        </is>
+      </c>
+      <c r="C76" s="15" t="inlineStr">
+        <is>
+          <t>New sitework: diesel portion broken out for separate RP reporting</t>
+        </is>
+      </c>
+      <c r="D76" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E76" s="15" t="inlineStr">
+        <is>
+          <t>Conditional field</t>
+        </is>
+      </c>
+      <c r="F76" s="15" t="inlineStr">
+        <is>
+          <t>IF new_sitework: diesel_sitework reported as separate RP component</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="42" customHeight="1">
+      <c r="A77" s="15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B77" s="15" t="inlineStr">
+        <is>
+          <t>Embodied — CapEx</t>
+        </is>
+      </c>
+      <c r="C77" s="15" t="inlineStr">
+        <is>
+          <t>Certify CapEx matches computed penalty</t>
+        </is>
+      </c>
+      <c r="D77" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E77" s="15" t="inlineStr">
+        <is>
+          <t>Cross-system match</t>
+        </is>
+      </c>
+      <c r="F77" s="15" t="inlineStr">
+        <is>
+          <t>certify_capex = calc_penalty</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="16" customHeight="1">
+      <c r="A78" s="12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B78" s="12" t="inlineStr">
+        <is>
+          <t>Embodied — Sitework</t>
+        </is>
+      </c>
+      <c r="C78" s="12" t="n"/>
+      <c r="D78" s="12" t="n"/>
+      <c r="E78" s="12" t="n"/>
+      <c r="F78" s="12" t="n"/>
+    </row>
+    <row r="79" ht="42" customHeight="1">
+      <c r="A79" s="13" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B79" s="13" t="inlineStr">
+        <is>
+          <t>Embodied — Sitework</t>
+        </is>
+      </c>
+      <c r="C79" s="13" t="inlineStr">
+        <is>
+          <t>All materials and processes documented</t>
+        </is>
+      </c>
+      <c r="D79" s="13" t="inlineStr">
+        <is>
+          <t>Charm Review</t>
+        </is>
+      </c>
+      <c r="E79" s="13" t="inlineStr">
+        <is>
+          <t>Document inventory</t>
+        </is>
+      </c>
+      <c r="F79" s="13" t="inlineStr">
+        <is>
+          <t>Requires reading documentation to confirm all scope items are captured</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="42" customHeight="1">
+      <c r="A80" s="13" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B80" s="13" t="inlineStr">
+        <is>
+          <t>Embodied — Sitework</t>
+        </is>
+      </c>
+      <c r="C80" s="13" t="inlineStr">
+        <is>
+          <t>All materials and processes included in calc</t>
+        </is>
+      </c>
+      <c r="D80" s="13" t="inlineStr">
+        <is>
+          <t>Charm Review</t>
+        </is>
+      </c>
+      <c r="E80" s="13" t="inlineStr">
+        <is>
+          <t>Document reading</t>
+        </is>
+      </c>
+      <c r="F80" s="13" t="inlineStr">
+        <is>
+          <t>Cross-check documentation list against calc sheet rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="42" customHeight="1">
+      <c r="A81" s="13" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B81" s="13" t="inlineStr">
+        <is>
+          <t>Embodied — Sitework</t>
+        </is>
+      </c>
+      <c r="C81" s="13" t="inlineStr">
+        <is>
+          <t>All emission factors cited and sourced</t>
+        </is>
+      </c>
+      <c r="D81" s="13" t="inlineStr">
+        <is>
+          <t>Charm Review</t>
+        </is>
+      </c>
+      <c r="E81" s="13" t="inlineStr">
+        <is>
+          <t>Evidence linking</t>
+        </is>
+      </c>
+      <c r="F81" s="13" t="inlineStr">
+        <is>
+          <t>Requires reading EF citations; cannot automate sourcing quality check</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="42" customHeight="1">
+      <c r="A82" s="13" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B82" s="13" t="inlineStr">
+        <is>
+          <t>Embodied — Sitework</t>
+        </is>
+      </c>
+      <c r="C82" s="13" t="inlineStr">
+        <is>
+          <t>All assumptions cited and sourced</t>
+        </is>
+      </c>
+      <c r="D82" s="13" t="inlineStr">
+        <is>
+          <t>Charm Review</t>
+        </is>
+      </c>
+      <c r="E82" s="13" t="inlineStr">
+        <is>
+          <t>Evidence linking</t>
+        </is>
+      </c>
+      <c r="F82" s="13" t="inlineStr">
+        <is>
+          <t>Requires reading assumption documentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="42" customHeight="1">
+      <c r="A83" s="15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B83" s="15" t="inlineStr">
+        <is>
+          <t>Embodied — Sitework</t>
+        </is>
+      </c>
+      <c r="C83" s="15" t="inlineStr">
+        <is>
+          <t>Diesel emissions clearly broken out from non-diesel</t>
+        </is>
+      </c>
+      <c r="D83" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E83" s="15" t="inlineStr">
+        <is>
+          <t>Field structure check</t>
+        </is>
+      </c>
+      <c r="F83" s="15" t="inlineStr">
+        <is>
+          <t>Two separate fields in calc; combined value = fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="42" customHeight="1">
+      <c r="A84" s="15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B84" s="15" t="inlineStr">
+        <is>
+          <t>Embodied — Sitework</t>
+        </is>
+      </c>
+      <c r="C84" s="15" t="inlineStr">
+        <is>
+          <t>Diesel portion reported as RP component (BCU-eligible)</t>
+        </is>
+      </c>
+      <c r="D84" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E84" s="15" t="inlineStr">
+        <is>
+          <t>Presence check</t>
+        </is>
+      </c>
+      <c r="F84" s="15" t="inlineStr">
+        <is>
+          <t>sitework_diesel_RP_component exists with non-zero value</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="42" customHeight="1">
+      <c r="A85" s="15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B85" s="15" t="inlineStr">
+        <is>
+          <t>Embodied — Sitework</t>
+        </is>
+      </c>
+      <c r="C85" s="15" t="inlineStr">
+        <is>
+          <t>Non-diesel added to CapEx inventory for amortization</t>
+        </is>
+      </c>
+      <c r="D85" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E85" s="15" t="inlineStr">
+        <is>
+          <t>Conditional arithmetic</t>
+        </is>
+      </c>
+      <c r="F85" s="15" t="inlineStr">
+        <is>
+          <t>non_diesel_GWP → capex_inventory row; verify transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="42" customHeight="1">
+      <c r="A86" s="15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B86" s="15" t="inlineStr">
+        <is>
+          <t>Embodied — Sitework</t>
+        </is>
+      </c>
+      <c r="C86" s="15" t="inlineStr">
+        <is>
+          <t>Non-diesel emissions netted against RP (not double-counted with CapEx amort)</t>
+        </is>
+      </c>
+      <c r="D86" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E86" s="15" t="inlineStr">
+        <is>
+          <t>Arithmetic</t>
+        </is>
+      </c>
+      <c r="F86" s="15" t="inlineStr">
+        <is>
+          <t>RP_sitework_net = diesel_only; non-diesel excluded from direct RP charge</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="42" customHeight="1">
+      <c r="A87" s="15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B87" s="15" t="inlineStr">
+        <is>
+          <t>Embodied — Sitework</t>
+        </is>
+      </c>
+      <c r="C87" s="15" t="inlineStr">
+        <is>
+          <t>All sitework emissions summed correctly</t>
+        </is>
+      </c>
+      <c r="D87" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E87" s="15" t="inlineStr">
+        <is>
+          <t>Arithmetic</t>
+        </is>
+      </c>
+      <c r="F87" s="15" t="inlineStr">
+        <is>
+          <t>total = Σ(diesel + non-diesel + all other sitework components)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="42" customHeight="1">
+      <c r="A88" s="15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B88" s="15" t="inlineStr">
+        <is>
+          <t>Embodied — Sitework</t>
+        </is>
+      </c>
+      <c r="C88" s="15" t="inlineStr">
+        <is>
+          <t>Certify sitework matches computed total</t>
+        </is>
+      </c>
+      <c r="D88" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E88" s="15" t="inlineStr">
+        <is>
+          <t>Cross-system match</t>
+        </is>
+      </c>
+      <c r="F88" s="15" t="inlineStr">
+        <is>
+          <t>certify_sitework = calc_total</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="16" customHeight="1">
+      <c r="A89" s="12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B89" s="12" t="inlineStr">
+        <is>
+          <t>Embodied — SP&amp;C</t>
+        </is>
+      </c>
+      <c r="C89" s="12" t="n"/>
+      <c r="D89" s="12" t="n"/>
+      <c r="E89" s="12" t="n"/>
+      <c r="F89" s="12" t="n"/>
+    </row>
+    <row r="90" ht="42" customHeight="1">
+      <c r="A90" s="13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B90" s="13" t="inlineStr">
+        <is>
+          <t>Embodied — SP&amp;C</t>
+        </is>
+      </c>
+      <c r="C90" s="13" t="inlineStr">
+        <is>
+          <t>Equipment list up to date for current operations</t>
+        </is>
+      </c>
+      <c r="D90" s="13" t="inlineStr">
+        <is>
+          <t>Charm Review</t>
+        </is>
+      </c>
+      <c r="E90" s="13" t="inlineStr">
+        <is>
+          <t>Judgment call</t>
+        </is>
+      </c>
+      <c r="F90" s="13" t="inlineStr">
+        <is>
+          <t>Requires reviewing list against known site configuration</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="42" customHeight="1">
+      <c r="A91" s="13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B91" s="13" t="inlineStr">
+        <is>
+          <t>Embodied — SP&amp;C</t>
+        </is>
+      </c>
+      <c r="C91" s="13" t="inlineStr">
+        <is>
+          <t>No missing or erroneous data in equipment list</t>
+        </is>
+      </c>
+      <c r="D91" s="13" t="inlineStr">
+        <is>
+          <t>Charm Review</t>
+        </is>
+      </c>
+      <c r="E91" s="13" t="inlineStr">
+        <is>
+          <t>Judgment call</t>
+        </is>
+      </c>
+      <c r="F91" s="13" t="inlineStr">
+        <is>
+          <t>Requires reading equipment list; 'erroneous' requires domain knowledge</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="42" customHeight="1">
+      <c r="A92" s="15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B92" s="15" t="inlineStr">
+        <is>
+          <t>Embodied — SP&amp;C</t>
+        </is>
+      </c>
+      <c r="C92" s="15" t="inlineStr">
+        <is>
+          <t>Weekly and RP penalties computed correctly</t>
+        </is>
+      </c>
+      <c r="D92" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E92" s="15" t="inlineStr">
+        <is>
+          <t>Arithmetic</t>
+        </is>
+      </c>
+      <c r="F92" s="15" t="inlineStr">
+        <is>
+          <t>weekly_penalty = pool × weekly_rate; RP_penalty = Σ(weekly_penalties in RP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="42" customHeight="1">
+      <c r="A93" s="15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B93" s="15" t="inlineStr">
+        <is>
+          <t>Embodied — SP&amp;C</t>
+        </is>
+      </c>
+      <c r="C93" s="15" t="inlineStr">
+        <is>
+          <t>Certify SP&amp;C matches computed RP penalty</t>
+        </is>
+      </c>
+      <c r="D93" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E93" s="15" t="inlineStr">
+        <is>
+          <t>Cross-system match</t>
+        </is>
+      </c>
+      <c r="F93" s="15" t="inlineStr">
+        <is>
+          <t>certify_spc = calc_RP_penalty</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="16" customHeight="1">
+      <c r="A94" s="12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B94" s="12" t="inlineStr">
+        <is>
+          <t>Railcar Cleaning &amp; Transport</t>
+        </is>
+      </c>
+      <c r="C94" s="12" t="n"/>
+      <c r="D94" s="12" t="n"/>
+      <c r="E94" s="12" t="n"/>
+      <c r="F94" s="12" t="n"/>
+    </row>
+    <row r="95" ht="42" customHeight="1">
+      <c r="A95" s="13" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B95" s="13" t="inlineStr">
+        <is>
+          <t>Railcar Cleaning &amp; Transport</t>
+        </is>
+      </c>
+      <c r="C95" s="13" t="inlineStr">
+        <is>
+          <t>All route distances have evidence in folder</t>
+        </is>
+      </c>
+      <c r="D95" s="13" t="inlineStr">
+        <is>
+          <t>Charm Review</t>
+        </is>
+      </c>
+      <c r="E95" s="13" t="inlineStr">
+        <is>
+          <t>Evidence linking</t>
+        </is>
+      </c>
+      <c r="F95" s="13" t="inlineStr">
+        <is>
+          <t>Requires confirming route docs (maps, distance records) attached per leg</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="42" customHeight="1">
+      <c r="A96" s="13" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B96" s="13" t="inlineStr">
+        <is>
+          <t>Railcar Cleaning &amp; Transport</t>
+        </is>
+      </c>
+      <c r="C96" s="13" t="inlineStr">
+        <is>
+          <t>All mass and distance inputs in calc sheet with evidence</t>
+        </is>
+      </c>
+      <c r="D96" s="13" t="inlineStr">
+        <is>
+          <t>Charm Review</t>
+        </is>
+      </c>
+      <c r="E96" s="13" t="inlineStr">
+        <is>
+          <t>Evidence linking</t>
+        </is>
+      </c>
+      <c r="F96" s="13" t="inlineStr">
+        <is>
+          <t>Requires reading calc sheet and confirming each input has a source</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="42" customHeight="1">
+      <c r="A97" s="15" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B97" s="15" t="inlineStr">
+        <is>
+          <t>Railcar Cleaning &amp; Transport</t>
+        </is>
+      </c>
+      <c r="C97" s="15" t="inlineStr">
+        <is>
+          <t>Cleaning emissions correctly computed</t>
+        </is>
+      </c>
+      <c r="D97" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E97" s="15" t="inlineStr">
+        <is>
+          <t>Arithmetic</t>
+        </is>
+      </c>
+      <c r="F97" s="15" t="inlineStr">
+        <is>
+          <t>cleaning_emiss = volume × cleaning_EF</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="42" customHeight="1">
+      <c r="A98" s="15" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B98" s="15" t="inlineStr">
+        <is>
+          <t>Railcar Cleaning &amp; Transport</t>
+        </is>
+      </c>
+      <c r="C98" s="15" t="inlineStr">
+        <is>
+          <t>Transport process emissions correct per leg (BCU-eligible)</t>
+        </is>
+      </c>
+      <c r="D98" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E98" s="15" t="inlineStr">
+        <is>
+          <t>Arithmetic</t>
+        </is>
+      </c>
+      <c r="F98" s="15" t="inlineStr">
+        <is>
+          <t>proc_emiss = mass × distance × process_EF per leg</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="42" customHeight="1">
+      <c r="A99" s="15" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B99" s="15" t="inlineStr">
+        <is>
+          <t>Railcar Cleaning &amp; Transport</t>
+        </is>
+      </c>
+      <c r="C99" s="15" t="inlineStr">
+        <is>
+          <t>Transport embodied emissions correct (NOT BCU-eligible)</t>
+        </is>
+      </c>
+      <c r="D99" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E99" s="15" t="inlineStr">
+        <is>
+          <t>Arithmetic</t>
+        </is>
+      </c>
+      <c r="F99" s="15" t="inlineStr">
+        <is>
+          <t>emb_emiss = distance × embodied_EF per leg</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="42" customHeight="1">
+      <c r="A100" s="15" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B100" s="15" t="inlineStr">
+        <is>
+          <t>Railcar Cleaning &amp; Transport</t>
+        </is>
+      </c>
+      <c r="C100" s="15" t="inlineStr">
+        <is>
+          <t>BCUs applied to process emissions only (not embodied or cleaning)</t>
+        </is>
+      </c>
+      <c r="D100" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E100" s="15" t="inlineStr">
+        <is>
+          <t>Eligibility rule</t>
+        </is>
+      </c>
+      <c r="F100" s="15" t="inlineStr">
+        <is>
+          <t>BCU[cleaning] = 0; BCU[embodied] = 0; only process eligible</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="42" customHeight="1">
+      <c r="A101" s="15" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B101" s="15" t="inlineStr">
+        <is>
+          <t>Railcar Cleaning &amp; Transport</t>
+        </is>
+      </c>
+      <c r="C101" s="15" t="inlineStr">
+        <is>
+          <t>Certify railcar values match calc sheet</t>
+        </is>
+      </c>
+      <c r="D101" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E101" s="15" t="inlineStr">
+        <is>
+          <t>Cross-system match</t>
+        </is>
+      </c>
+      <c r="F101" s="15" t="inlineStr">
+        <is>
+          <t>certify_railcar = calc_railcar for each component</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="42" customHeight="1">
+      <c r="A102" s="15" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B102" s="15" t="inlineStr">
+        <is>
+          <t>Railcar Cleaning &amp; Transport</t>
+        </is>
+      </c>
+      <c r="C102" s="15" t="inlineStr">
+        <is>
+          <t>BCU amounts match BCU Quant sheet</t>
+        </is>
+      </c>
+      <c r="D102" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E102" s="15" t="inlineStr">
+        <is>
+          <t>Cross-sheet match</t>
+        </is>
+      </c>
+      <c r="F102" s="15" t="inlineStr">
+        <is>
+          <t>certify_BCU[railcar] = BCU_quant_sheet[railcar]; line-by-line trace</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="16" customHeight="1">
+      <c r="A103" s="12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B103" s="12" t="inlineStr">
+        <is>
+          <t>Waste Disposal</t>
+        </is>
+      </c>
+      <c r="C103" s="12" t="n"/>
+      <c r="D103" s="12" t="n"/>
+      <c r="E103" s="12" t="n"/>
+      <c r="F103" s="12" t="n"/>
+    </row>
+    <row r="104" ht="42" customHeight="1">
+      <c r="A104" s="13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B104" s="13" t="inlineStr">
+        <is>
+          <t>Waste Disposal</t>
+        </is>
+      </c>
+      <c r="C104" s="13" t="inlineStr">
+        <is>
+          <t>Documentation for all disposal events present in evidence folder</t>
+        </is>
+      </c>
+      <c r="D104" s="13" t="inlineStr">
+        <is>
+          <t>Charm Review</t>
+        </is>
+      </c>
+      <c r="E104" s="13" t="inlineStr">
+        <is>
+          <t>Document inventory</t>
+        </is>
+      </c>
+      <c r="F104" s="13" t="inlineStr">
+        <is>
+          <t>Requires confirming disposal records exist for every disposal event in period</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="42" customHeight="1">
+      <c r="A105" s="13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B105" s="13" t="inlineStr">
+        <is>
+          <t>Waste Disposal</t>
+        </is>
+      </c>
+      <c r="C105" s="13" t="inlineStr">
+        <is>
+          <t>Route distance documentation present (may be multiple destinations)</t>
+        </is>
+      </c>
+      <c r="D105" s="13" t="inlineStr">
+        <is>
+          <t>Charm Review</t>
+        </is>
+      </c>
+      <c r="E105" s="13" t="inlineStr">
+        <is>
+          <t>Evidence linking</t>
+        </is>
+      </c>
+      <c r="F105" s="13" t="inlineStr">
+        <is>
+          <t>Requires confirming route docs attached per destination</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="42" customHeight="1">
+      <c r="A106" s="13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B106" s="13" t="inlineStr">
+        <is>
+          <t>Waste Disposal</t>
+        </is>
+      </c>
+      <c r="C106" s="13" t="inlineStr">
+        <is>
+          <t>All disposal events in calc sheet</t>
+        </is>
+      </c>
+      <c r="D106" s="13" t="inlineStr">
+        <is>
+          <t>Charm Review</t>
+        </is>
+      </c>
+      <c r="E106" s="13" t="inlineStr">
+        <is>
+          <t>Document reading</t>
+        </is>
+      </c>
+      <c r="F106" s="13" t="inlineStr">
+        <is>
+          <t>Requires reading calc sheet against disposal records</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="42" customHeight="1">
+      <c r="A107" s="15" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B107" s="15" t="inlineStr">
+        <is>
+          <t>Waste Disposal</t>
+        </is>
+      </c>
+      <c r="C107" s="15" t="inlineStr">
+        <is>
+          <t>Per-event transport process emissions correct (BCU-eligible)</t>
+        </is>
+      </c>
+      <c r="D107" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E107" s="15" t="inlineStr">
+        <is>
+          <t>Arithmetic</t>
+        </is>
+      </c>
+      <c r="F107" s="15" t="inlineStr">
+        <is>
+          <t>proc = mass × distance × process_EF</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="42" customHeight="1">
+      <c r="A108" s="15" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B108" s="15" t="inlineStr">
+        <is>
+          <t>Waste Disposal</t>
+        </is>
+      </c>
+      <c r="C108" s="15" t="inlineStr">
+        <is>
+          <t>Per-event transport embodied emissions correct (NOT BCU-eligible)</t>
+        </is>
+      </c>
+      <c r="D108" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E108" s="15" t="inlineStr">
+        <is>
+          <t>Arithmetic</t>
+        </is>
+      </c>
+      <c r="F108" s="15" t="inlineStr">
+        <is>
+          <t>emb = distance × embodied_EF</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="42" customHeight="1">
+      <c r="A109" s="15" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B109" s="15" t="inlineStr">
+        <is>
+          <t>Waste Disposal</t>
+        </is>
+      </c>
+      <c r="C109" s="15" t="inlineStr">
+        <is>
+          <t>Per-event disposal EF correctly chosen for physical disposal method</t>
+        </is>
+      </c>
+      <c r="D109" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E109" s="15" t="inlineStr">
+        <is>
+          <t>Lookup / reference</t>
+        </is>
+      </c>
+      <c r="F109" s="15" t="inlineStr">
+        <is>
+          <t>EF = lookup(disposal_method); wrong method = fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="42" customHeight="1">
+      <c r="A110" s="15" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B110" s="15" t="inlineStr">
+        <is>
+          <t>Waste Disposal</t>
+        </is>
+      </c>
+      <c r="C110" s="15" t="inlineStr">
+        <is>
+          <t>Per-event disposal emissions correct</t>
+        </is>
+      </c>
+      <c r="D110" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E110" s="15" t="inlineStr">
+        <is>
+          <t>Arithmetic</t>
+        </is>
+      </c>
+      <c r="F110" s="15" t="inlineStr">
+        <is>
+          <t>disposal_emiss = mass × disposal_EF</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="42" customHeight="1">
+      <c r="A111" s="15" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B111" s="15" t="inlineStr">
+        <is>
+          <t>Waste Disposal</t>
+        </is>
+      </c>
+      <c r="C111" s="15" t="inlineStr">
+        <is>
+          <t>Upstream emissions included if bio-oil or contaminated material disposed</t>
+        </is>
+      </c>
+      <c r="D111" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E111" s="15" t="inlineStr">
+        <is>
+          <t>Conditional arithmetic</t>
+        </is>
+      </c>
+      <c r="F111" s="15" t="inlineStr">
+        <is>
+          <t>IF material = bio-oil: upstream = production_CI × transport_to_last_point</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="42" customHeight="1">
+      <c r="A112" s="15" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B112" s="15" t="inlineStr">
+        <is>
+          <t>Waste Disposal</t>
+        </is>
+      </c>
+      <c r="C112" s="15" t="inlineStr">
+        <is>
+          <t>If upstream: production CI matches relevant production period</t>
+        </is>
+      </c>
+      <c r="D112" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E112" s="15" t="inlineStr">
+        <is>
+          <t>Cross-field match</t>
+        </is>
+      </c>
+      <c r="F112" s="15" t="inlineStr">
+        <is>
+          <t>upstream_CI = CI[production_period] from approved source</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="42" customHeight="1">
+      <c r="A113" s="15" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B113" s="15" t="inlineStr">
+        <is>
+          <t>Waste Disposal</t>
+        </is>
+      </c>
+      <c r="C113" s="15" t="inlineStr">
+        <is>
+          <t>If upstream: transport to last point of residence correctly computed</t>
+        </is>
+      </c>
+      <c r="D113" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E113" s="15" t="inlineStr">
+        <is>
+          <t>Arithmetic</t>
+        </is>
+      </c>
+      <c r="F113" s="15" t="inlineStr">
+        <is>
+          <t>transport_upstream = mass × distance_to_last_point × EF</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="42" customHeight="1">
+      <c r="A114" s="15" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B114" s="15" t="inlineStr">
+        <is>
+          <t>Waste Disposal</t>
+        </is>
+      </c>
+      <c r="C114" s="15" t="inlineStr">
+        <is>
+          <t>Total = transport process + transport embodied + disposal + upstream (where applicable)</t>
+        </is>
+      </c>
+      <c r="D114" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E114" s="15" t="inlineStr">
+        <is>
+          <t>Arithmetic</t>
+        </is>
+      </c>
+      <c r="F114" s="15" t="inlineStr">
+        <is>
+          <t>event_total = proc + emb + disposal + upstream</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="42" customHeight="1">
+      <c r="A115" s="15" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B115" s="15" t="inlineStr">
+        <is>
+          <t>Waste Disposal</t>
+        </is>
+      </c>
+      <c r="C115" s="15" t="inlineStr">
+        <is>
+          <t>Certify waste disposal matches calc total</t>
+        </is>
+      </c>
+      <c r="D115" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E115" s="15" t="inlineStr">
+        <is>
+          <t>Cross-system match</t>
+        </is>
+      </c>
+      <c r="F115" s="15" t="inlineStr">
+        <is>
+          <t>certify_waste = calc_total</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="16" customHeight="1">
+      <c r="A116" s="12" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B116" s="12" t="inlineStr">
+        <is>
+          <t>Additional Transport</t>
+        </is>
+      </c>
+      <c r="C116" s="12" t="n"/>
+      <c r="D116" s="12" t="n"/>
+      <c r="E116" s="12" t="n"/>
+      <c r="F116" s="12" t="n"/>
+    </row>
+    <row r="117" ht="42" customHeight="1">
+      <c r="A117" s="13" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B117" s="13" t="inlineStr">
+        <is>
+          <t>Additional Transport</t>
+        </is>
+      </c>
+      <c r="C117" s="13" t="inlineStr">
+        <is>
+          <t>All route distances have evidence in folder</t>
+        </is>
+      </c>
+      <c r="D117" s="13" t="inlineStr">
+        <is>
+          <t>Charm Review</t>
+        </is>
+      </c>
+      <c r="E117" s="13" t="inlineStr">
+        <is>
+          <t>Evidence linking</t>
+        </is>
+      </c>
+      <c r="F117" s="13" t="inlineStr">
+        <is>
+          <t>Requires confirming route docs attached per movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="42" customHeight="1">
+      <c r="A118" s="13" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B118" s="13" t="inlineStr">
+        <is>
+          <t>Additional Transport</t>
+        </is>
+      </c>
+      <c r="C118" s="13" t="inlineStr">
+        <is>
+          <t>All mass and distance inputs in calc with evidence</t>
+        </is>
+      </c>
+      <c r="D118" s="13" t="inlineStr">
+        <is>
+          <t>Charm Review</t>
+        </is>
+      </c>
+      <c r="E118" s="13" t="inlineStr">
+        <is>
+          <t>Evidence linking</t>
+        </is>
+      </c>
+      <c r="F118" s="13" t="inlineStr">
+        <is>
+          <t>Requires reading calc inputs and confirming source for each</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="42" customHeight="1">
+      <c r="A119" s="15" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B119" s="15" t="inlineStr">
+        <is>
+          <t>Additional Transport</t>
+        </is>
+      </c>
+      <c r="C119" s="15" t="inlineStr">
+        <is>
+          <t>Transport fuel type identified (determines BCU eligibility)</t>
+        </is>
+      </c>
+      <c r="D119" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E119" s="15" t="inlineStr">
+        <is>
+          <t>Presence check</t>
+        </is>
+      </c>
+      <c r="F119" s="15" t="inlineStr">
+        <is>
+          <t>fuel_type field non-null; required to determine eligibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="42" customHeight="1">
+      <c r="A120" s="15" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B120" s="15" t="inlineStr">
+        <is>
+          <t>Additional Transport</t>
+        </is>
+      </c>
+      <c r="C120" s="15" t="inlineStr">
+        <is>
+          <t>If diesel: process BCU-eligible; embodied NOT eligible</t>
+        </is>
+      </c>
+      <c r="D120" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E120" s="15" t="inlineStr">
+        <is>
+          <t>Eligibility rule</t>
+        </is>
+      </c>
+      <c r="F120" s="15" t="inlineStr">
+        <is>
+          <t>conditional on fuel_type = diesel</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="42" customHeight="1">
+      <c r="A121" s="15" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B121" s="15" t="inlineStr">
+        <is>
+          <t>Additional Transport</t>
+        </is>
+      </c>
+      <c r="C121" s="15" t="inlineStr">
+        <is>
+          <t>If non-diesel: NO BCU eligibility for any component</t>
+        </is>
+      </c>
+      <c r="D121" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E121" s="15" t="inlineStr">
+        <is>
+          <t>Eligibility rule</t>
+        </is>
+      </c>
+      <c r="F121" s="15" t="inlineStr">
+        <is>
+          <t>conditional on fuel_type ≠ diesel; BCU = 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="42" customHeight="1">
+      <c r="A122" s="15" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B122" s="15" t="inlineStr">
+        <is>
+          <t>Additional Transport</t>
+        </is>
+      </c>
+      <c r="C122" s="15" t="inlineStr">
+        <is>
+          <t>Certify additional transport matches calc</t>
+        </is>
+      </c>
+      <c r="D122" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E122" s="15" t="inlineStr">
+        <is>
+          <t>Cross-system match</t>
+        </is>
+      </c>
+      <c r="F122" s="15" t="inlineStr">
+        <is>
+          <t>certify_add_transport = calc_total</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="16" customHeight="1">
+      <c r="A123" s="12" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B123" s="12" t="inlineStr">
+        <is>
+          <t>Pump Oil (Conditional)</t>
+        </is>
+      </c>
+      <c r="C123" s="12" t="n"/>
+      <c r="D123" s="12" t="n"/>
+      <c r="E123" s="12" t="n"/>
+      <c r="F123" s="12" t="n"/>
+    </row>
+    <row r="124" ht="42" customHeight="1">
+      <c r="A124" s="13" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B124" s="13" t="inlineStr">
+        <is>
+          <t>Pump Oil (Conditional)</t>
+        </is>
+      </c>
+      <c r="C124" s="13" t="inlineStr">
+        <is>
+          <t>Receipts present in folder OR confirmed no purchase this RP (→ N/A)</t>
+        </is>
+      </c>
+      <c r="D124" s="13" t="inlineStr">
+        <is>
+          <t>Charm Review</t>
+        </is>
+      </c>
+      <c r="E124" s="13" t="inlineStr">
+        <is>
+          <t>Document inventory</t>
+        </is>
+      </c>
+      <c r="F124" s="13" t="inlineStr">
+        <is>
+          <t>Confirm either receipts exist or N/A documented; blank = flag</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="42" customHeight="1">
+      <c r="A125" s="13" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B125" s="13" t="inlineStr">
+        <is>
+          <t>Pump Oil (Conditional)</t>
+        </is>
+      </c>
+      <c r="C125" s="13" t="inlineStr">
+        <is>
+          <t>All pump oil receipts in calc sheet (if applicable)</t>
+        </is>
+      </c>
+      <c r="D125" s="13" t="inlineStr">
+        <is>
+          <t>Charm Review</t>
+        </is>
+      </c>
+      <c r="E125" s="13" t="inlineStr">
+        <is>
+          <t>Document reading</t>
+        </is>
+      </c>
+      <c r="F125" s="13" t="inlineStr">
+        <is>
+          <t>Requires reading calc sheet against receipts</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="42" customHeight="1">
+      <c r="A126" s="15" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B126" s="15" t="inlineStr">
+        <is>
+          <t>Pump Oil (Conditional)</t>
+        </is>
+      </c>
+      <c r="C126" s="15" t="inlineStr">
+        <is>
+          <t>Math correct in pump oil calc</t>
+        </is>
+      </c>
+      <c r="D126" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E126" s="15" t="inlineStr">
+        <is>
+          <t>Arithmetic</t>
+        </is>
+      </c>
+      <c r="F126" s="15" t="inlineStr">
+        <is>
+          <t>volume × density × EF = emissions</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="16" customHeight="1">
+      <c r="A127" s="12" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B127" s="12" t="inlineStr">
+        <is>
+          <t>LCS (Conditional)</t>
+        </is>
+      </c>
+      <c r="C127" s="12" t="n"/>
+      <c r="D127" s="12" t="n"/>
+      <c r="E127" s="12" t="n"/>
+      <c r="F127" s="12" t="n"/>
+    </row>
+    <row r="128" ht="42" customHeight="1">
+      <c r="A128" s="13" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B128" s="13" t="inlineStr">
+        <is>
+          <t>LCS (Conditional)</t>
+        </is>
+      </c>
+      <c r="C128" s="13" t="inlineStr">
+        <is>
+          <t>Receipts present in folder OR confirmed not in process (→ N/A)</t>
+        </is>
+      </c>
+      <c r="D128" s="13" t="inlineStr">
+        <is>
+          <t>Charm Review</t>
+        </is>
+      </c>
+      <c r="E128" s="13" t="inlineStr">
+        <is>
+          <t>Document inventory</t>
+        </is>
+      </c>
+      <c r="F128" s="13" t="inlineStr">
+        <is>
+          <t>Confirm either receipts exist or N/A documented</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="42" customHeight="1">
+      <c r="A129" s="15" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B129" s="15" t="inlineStr">
+        <is>
+          <t>LCS (Conditional)</t>
+        </is>
+      </c>
+      <c r="C129" s="15" t="inlineStr">
+        <is>
+          <t>All receipts in calc; transport distance, mass, emissions correct</t>
+        </is>
+      </c>
+      <c r="D129" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E129" s="15" t="inlineStr">
+        <is>
+          <t>Cross-field match + arithmetic</t>
+        </is>
+      </c>
+      <c r="F129" s="15" t="inlineStr">
+        <is>
+          <t>Receipts → mass in calc; distance = route_lookup; emissions = mass × dist × EF</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="16" customHeight="1">
+      <c r="A130" s="12" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B130" s="12" t="inlineStr">
+        <is>
+          <t>Production / Inventory Reconciliation</t>
+        </is>
+      </c>
+      <c r="C130" s="12" t="n"/>
+      <c r="D130" s="12" t="n"/>
+      <c r="E130" s="12" t="n"/>
+      <c r="F130" s="12" t="n"/>
+    </row>
+    <row r="131" ht="42" customHeight="1">
+      <c r="A131" s="13" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B131" s="13" t="inlineStr">
+        <is>
+          <t>Production / Inventory Reconciliation</t>
+        </is>
+      </c>
+      <c r="C131" s="13" t="inlineStr">
+        <is>
+          <t>Reconciliation documentation present</t>
+        </is>
+      </c>
+      <c r="D131" s="13" t="inlineStr">
+        <is>
+          <t>Charm Review</t>
+        </is>
+      </c>
+      <c r="E131" s="13" t="inlineStr">
+        <is>
+          <t>Document inventory</t>
+        </is>
+      </c>
+      <c r="F131" s="13" t="inlineStr">
+        <is>
+          <t>Confirm reconciliation spreadsheet exists for the annual cycle</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="42" customHeight="1">
+      <c r="A132" s="13" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B132" s="13" t="inlineStr">
+        <is>
+          <t>Production / Inventory Reconciliation</t>
+        </is>
+      </c>
+      <c r="C132" s="13" t="inlineStr">
+        <is>
+          <t>Outstanding oil quantities correctly identified from production vs. shipment</t>
+        </is>
+      </c>
+      <c r="D132" s="13" t="inlineStr">
+        <is>
+          <t>Charm Review</t>
+        </is>
+      </c>
+      <c r="E132" s="13" t="inlineStr">
+        <is>
+          <t>Document reading</t>
+        </is>
+      </c>
+      <c r="F132" s="13" t="inlineStr">
+        <is>
+          <t>Requires reading production records and shipment logs; not yet structured data</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="42" customHeight="1">
+      <c r="A133" s="15" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B133" s="15" t="inlineStr">
+        <is>
+          <t>Production / Inventory Reconciliation</t>
+        </is>
+      </c>
+      <c r="C133" s="15" t="inlineStr">
+        <is>
+          <t>CI for each production period and oil type correctly applied</t>
+        </is>
+      </c>
+      <c r="D133" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E133" s="15" t="inlineStr">
+        <is>
+          <t>Cross-field match</t>
+        </is>
+      </c>
+      <c r="F133" s="15" t="inlineStr">
+        <is>
+          <t>CI[PP][oil_type] from approved PP Summary; mismatch = fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="42" customHeight="1">
+      <c r="A134" s="15" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B134" s="15" t="inlineStr">
+        <is>
+          <t>Production / Inventory Reconciliation</t>
+        </is>
+      </c>
+      <c r="C134" s="15" t="inlineStr">
+        <is>
+          <t>For exhausted inventory: reconciliation emission computed</t>
+        </is>
+      </c>
+      <c r="D134" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E134" s="15" t="inlineStr">
+        <is>
+          <t>Conditional arithmetic</t>
+        </is>
+      </c>
+      <c r="F134" s="15" t="inlineStr">
+        <is>
+          <t>IF inventory_exhausted: reconcile_emiss = outstanding_mass × CI</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="42" customHeight="1">
+      <c r="A135" s="15" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B135" s="15" t="inlineStr">
+        <is>
+          <t>Production / Inventory Reconciliation</t>
+        </is>
+      </c>
+      <c r="C135" s="15" t="inlineStr">
+        <is>
+          <t>Reconciliation emissions included in site total</t>
+        </is>
+      </c>
+      <c r="D135" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E135" s="15" t="inlineStr">
+        <is>
+          <t>Arithmetic</t>
+        </is>
+      </c>
+      <c r="F135" s="15" t="inlineStr">
+        <is>
+          <t>site_total includes reconcile_emiss; omission = fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="42" customHeight="1">
+      <c r="A136" s="15" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B136" s="15" t="inlineStr">
+        <is>
+          <t>Production / Inventory Reconciliation</t>
+        </is>
+      </c>
+      <c r="C136" s="15" t="inlineStr">
+        <is>
+          <t>Certify reconciliation component matches computed value</t>
+        </is>
+      </c>
+      <c r="D136" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E136" s="15" t="inlineStr">
+        <is>
+          <t>Cross-system match</t>
+        </is>
+      </c>
+      <c r="F136" s="15" t="inlineStr">
+        <is>
+          <t>certify_reconcile = calc_reconcile</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="16" customHeight="1">
+      <c r="A137" s="12" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B137" s="12" t="inlineStr">
+        <is>
+          <t>One-Off / Nonstandard</t>
+        </is>
+      </c>
+      <c r="C137" s="12" t="n"/>
+      <c r="D137" s="12" t="n"/>
+      <c r="E137" s="12" t="n"/>
+      <c r="F137" s="12" t="n"/>
+    </row>
+    <row r="138" ht="42" customHeight="1">
+      <c r="A138" s="13" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B138" s="13" t="inlineStr">
+        <is>
+          <t>One-Off / Nonstandard</t>
+        </is>
+      </c>
+      <c r="C138" s="13" t="inlineStr">
+        <is>
+          <t>One-off subfolders identified and documented</t>
+        </is>
+      </c>
+      <c r="D138" s="13" t="inlineStr">
+        <is>
+          <t>Charm Review</t>
+        </is>
+      </c>
+      <c r="E138" s="13" t="inlineStr">
+        <is>
+          <t>Document inventory</t>
+        </is>
+      </c>
+      <c r="F138" s="13" t="inlineStr">
+        <is>
+          <t>Requires reviewing folder structure for any non-standard emission event</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="42" customHeight="1">
+      <c r="A139" s="13" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B139" s="13" t="inlineStr">
+        <is>
+          <t>One-Off / Nonstandard</t>
+        </is>
+      </c>
+      <c r="C139" s="13" t="inlineStr">
+        <is>
+          <t>Per one-off: quantification methodology clearly documented</t>
+        </is>
+      </c>
+      <c r="D139" s="13" t="inlineStr">
+        <is>
+          <t>Charm Review</t>
+        </is>
+      </c>
+      <c r="E139" s="13" t="inlineStr">
+        <is>
+          <t>Document reading</t>
+        </is>
+      </c>
+      <c r="F139" s="13" t="inlineStr">
+        <is>
+          <t>Judgment on documentation quality; cannot be automated</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="42" customHeight="1">
+      <c r="A140" s="13" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B140" s="13" t="inlineStr">
+        <is>
+          <t>One-Off / Nonstandard</t>
+        </is>
+      </c>
+      <c r="C140" s="13" t="inlineStr">
+        <is>
+          <t>Per one-off: all EFs cited and sourced</t>
+        </is>
+      </c>
+      <c r="D140" s="13" t="inlineStr">
+        <is>
+          <t>Charm Review</t>
+        </is>
+      </c>
+      <c r="E140" s="13" t="inlineStr">
+        <is>
+          <t>Evidence linking</t>
+        </is>
+      </c>
+      <c r="F140" s="13" t="inlineStr">
+        <is>
+          <t>Requires reading citations in one-off calc sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="42" customHeight="1">
+      <c r="A141" s="13" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B141" s="13" t="inlineStr">
+        <is>
+          <t>One-Off / Nonstandard</t>
+        </is>
+      </c>
+      <c r="C141" s="13" t="inlineStr">
+        <is>
+          <t>Per one-off: all assumptions documented</t>
+        </is>
+      </c>
+      <c r="D141" s="13" t="inlineStr">
+        <is>
+          <t>Charm Review</t>
+        </is>
+      </c>
+      <c r="E141" s="13" t="inlineStr">
+        <is>
+          <t>Document reading</t>
+        </is>
+      </c>
+      <c r="F141" s="13" t="inlineStr">
+        <is>
+          <t>Requires reading assumption documentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="42" customHeight="1">
+      <c r="A142" s="15" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B142" s="15" t="inlineStr">
+        <is>
+          <t>One-Off / Nonstandard</t>
+        </is>
+      </c>
+      <c r="C142" s="15" t="inlineStr">
+        <is>
+          <t>Per one-off: calculations correct</t>
+        </is>
+      </c>
+      <c r="D142" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E142" s="15" t="inlineStr">
+        <is>
+          <t>Arithmetic</t>
+        </is>
+      </c>
+      <c r="F142" s="15" t="inlineStr">
+        <is>
+          <t>Check formula chain in one-off calc sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="42" customHeight="1">
+      <c r="A143" s="15" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B143" s="15" t="inlineStr">
+        <is>
+          <t>One-Off / Nonstandard</t>
+        </is>
+      </c>
+      <c r="C143" s="15" t="inlineStr">
+        <is>
+          <t>Per one-off: Certify component matches quantification</t>
+        </is>
+      </c>
+      <c r="D143" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E143" s="15" t="inlineStr">
+        <is>
+          <t>Cross-system match</t>
+        </is>
+      </c>
+      <c r="F143" s="15" t="inlineStr">
+        <is>
+          <t>certify_oneoff = calc_oneoff</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="42" customHeight="1">
+      <c r="A144" s="13" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B144" s="13" t="inlineStr">
+        <is>
+          <t>One-Off / Nonstandard</t>
+        </is>
+      </c>
+      <c r="C144" s="13" t="inlineStr">
+        <is>
+          <t>If lump sum: supporting quantification spreadsheet present</t>
+        </is>
+      </c>
+      <c r="D144" s="13" t="inlineStr">
+        <is>
+          <t>Charm Review</t>
+        </is>
+      </c>
+      <c r="E144" s="13" t="inlineStr">
+        <is>
+          <t>Document inventory</t>
+        </is>
+      </c>
+      <c r="F144" s="13" t="inlineStr">
+        <is>
+          <t>Confirm supporting spreadsheet attached</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="16" customHeight="1">
+      <c r="A145" s="12" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B145" s="12" t="inlineStr">
+        <is>
+          <t>BCU / REC Offsets</t>
+        </is>
+      </c>
+      <c r="C145" s="12" t="n"/>
+      <c r="D145" s="12" t="n"/>
+      <c r="E145" s="12" t="n"/>
+      <c r="F145" s="12" t="n"/>
+    </row>
+    <row r="146" ht="42" customHeight="1">
+      <c r="A146" s="13" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B146" s="13" t="inlineStr">
+        <is>
+          <t>BCU / REC Offsets</t>
+        </is>
+      </c>
+      <c r="C146" s="13" t="inlineStr">
+        <is>
+          <t>BCU Quant sheet present for this RP</t>
+        </is>
+      </c>
+      <c r="D146" s="13" t="inlineStr">
+        <is>
+          <t>Charm Review</t>
+        </is>
+      </c>
+      <c r="E146" s="13" t="inlineStr">
+        <is>
+          <t>Document inventory</t>
+        </is>
+      </c>
+      <c r="F146" s="13" t="inlineStr">
+        <is>
+          <t>Confirm BCU Quant .xlsx exists for the RP</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="42" customHeight="1">
+      <c r="A147" s="15" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B147" s="15" t="inlineStr">
+        <is>
+          <t>BCU / REC Offsets</t>
+        </is>
+      </c>
+      <c r="C147" s="15" t="inlineStr">
+        <is>
+          <t>Every site-emission BCU in Certify traces to a quant sheet line</t>
+        </is>
+      </c>
+      <c r="D147" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E147" s="15" t="inlineStr">
+        <is>
+          <t>Cross-sheet match</t>
+        </is>
+      </c>
+      <c r="F147" s="15" t="inlineStr">
+        <is>
+          <t>Each Certify BCU entry has matching row in BCU Quant sheet; orphan = fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="42" customHeight="1">
+      <c r="A148" s="15" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B148" s="15" t="inlineStr">
+        <is>
+          <t>BCU / REC Offsets</t>
+        </is>
+      </c>
+      <c r="C148" s="15" t="inlineStr">
+        <is>
+          <t>Site-emission BCU quantities reconciled (trace line-by-line; Certify totals mix batch + site)</t>
+        </is>
+      </c>
+      <c r="D148" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E148" s="15" t="inlineStr">
+        <is>
+          <t>Cross-sheet match</t>
+        </is>
+      </c>
+      <c r="F148" s="15" t="inlineStr">
+        <is>
+          <t>Line-by-line match required; aggregate match insufficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="42" customHeight="1">
+      <c r="A149" s="15" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B149" s="15" t="inlineStr">
+        <is>
+          <t>BCU / REC Offsets</t>
+        </is>
+      </c>
+      <c r="C149" s="15" t="inlineStr">
+        <is>
+          <t>BCU allocation correct — eligible components only</t>
+        </is>
+      </c>
+      <c r="D149" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E149" s="15" t="inlineStr">
+        <is>
+          <t>Eligibility rule</t>
+        </is>
+      </c>
+      <c r="F149" s="15" t="inlineStr">
+        <is>
+          <t>BCU applied only to: diesel consumption, diesel delivery process, brine process, railcar process</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="42" customHeight="1">
+      <c r="A150" s="15" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B150" s="15" t="inlineStr">
+        <is>
+          <t>BCU / REC Offsets</t>
+        </is>
+      </c>
+      <c r="C150" s="15" t="inlineStr">
+        <is>
+          <t>NO BCUs on ineligible components (embodied, gasoline, SAF, electricity, cleaning)</t>
+        </is>
+      </c>
+      <c r="D150" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E150" s="15" t="inlineStr">
+        <is>
+          <t>Absence check</t>
+        </is>
+      </c>
+      <c r="F150" s="15" t="inlineStr">
+        <is>
+          <t>BCU = 0 for: all embodied, gasoline, SAF, electricity, cleaning; non-zero = fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="42" customHeight="1">
+      <c r="A151" s="15" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B151" s="15" t="inlineStr">
+        <is>
+          <t>BCU / REC Offsets</t>
+        </is>
+      </c>
+      <c r="C151" s="15" t="inlineStr">
+        <is>
+          <t>REC kWh matches consumed electricity kWh for all relevant components</t>
+        </is>
+      </c>
+      <c r="D151" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E151" s="15" t="inlineStr">
+        <is>
+          <t>Equality check</t>
+        </is>
+      </c>
+      <c r="F151" s="15" t="inlineStr">
+        <is>
+          <t>REC_kWh = consumed_kWh; mismatch = fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="42" customHeight="1">
+      <c r="A152" s="13" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B152" s="13" t="inlineStr">
+        <is>
+          <t>BCU / REC Offsets</t>
+        </is>
+      </c>
+      <c r="C152" s="13" t="inlineStr">
+        <is>
+          <t>EAC inventory updated for this RP</t>
+        </is>
+      </c>
+      <c r="D152" s="13" t="inlineStr">
+        <is>
+          <t>Charm Review</t>
+        </is>
+      </c>
+      <c r="E152" s="13" t="inlineStr">
+        <is>
+          <t>Document reading</t>
+        </is>
+      </c>
+      <c r="F152" s="13" t="inlineStr">
+        <is>
+          <t>Requires reading EAC inventory to confirm current RP entries added</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="16" customHeight="1">
+      <c r="A153" s="12" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B153" s="12" t="inlineStr">
+        <is>
+          <t>Emission Factor Validation</t>
+        </is>
+      </c>
+      <c r="C153" s="12" t="n"/>
+      <c r="D153" s="12" t="n"/>
+      <c r="E153" s="12" t="n"/>
+      <c r="F153" s="12" t="n"/>
+    </row>
+    <row r="154" ht="42" customHeight="1">
+      <c r="A154" s="13" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B154" s="13" t="inlineStr">
+        <is>
+          <t>Emission Factor Validation</t>
+        </is>
+      </c>
+      <c r="C154" s="13" t="inlineStr">
+        <is>
+          <t>Standard EF spreadsheet present and version-controlled for current year</t>
+        </is>
+      </c>
+      <c r="D154" s="13" t="inlineStr">
+        <is>
+          <t>Charm Review</t>
+        </is>
+      </c>
+      <c r="E154" s="13" t="inlineStr">
+        <is>
+          <t>Document inventory</t>
+        </is>
+      </c>
+      <c r="F154" s="13" t="inlineStr">
+        <is>
+          <t>Confirm current-year EF file exists and is versioned</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="42" customHeight="1">
+      <c r="A155" s="15" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B155" s="15" t="inlineStr">
+        <is>
+          <t>Emission Factor Validation</t>
+        </is>
+      </c>
+      <c r="C155" s="15" t="inlineStr">
+        <is>
+          <t>Diesel EF matches current year standard</t>
+        </is>
+      </c>
+      <c r="D155" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E155" s="15" t="inlineStr">
+        <is>
+          <t>Lookup / reference</t>
+        </is>
+      </c>
+      <c r="F155" s="15" t="inlineStr">
+        <is>
+          <t>EF = lookup(fuel='diesel', year=current)</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="42" customHeight="1">
+      <c r="A156" s="15" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B156" s="15" t="inlineStr">
+        <is>
+          <t>Emission Factor Validation</t>
+        </is>
+      </c>
+      <c r="C156" s="15" t="inlineStr">
+        <is>
+          <t>Gasoline EF matches current year standard</t>
+        </is>
+      </c>
+      <c r="D156" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E156" s="15" t="inlineStr">
+        <is>
+          <t>Lookup / reference</t>
+        </is>
+      </c>
+      <c r="F156" s="15" t="inlineStr">
+        <is>
+          <t>EF = lookup(fuel='gasoline', year=current)</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="42" customHeight="1">
+      <c r="A157" s="15" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B157" s="15" t="inlineStr">
+        <is>
+          <t>Emission Factor Validation</t>
+        </is>
+      </c>
+      <c r="C157" s="15" t="inlineStr">
+        <is>
+          <t>Methanol EF matches current year standard</t>
+        </is>
+      </c>
+      <c r="D157" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E157" s="15" t="inlineStr">
+        <is>
+          <t>Lookup / reference</t>
+        </is>
+      </c>
+      <c r="F157" s="15" t="inlineStr">
+        <is>
+          <t>EF = lookup(fuel='methanol', year=current)</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="42" customHeight="1">
+      <c r="A158" s="15" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B158" s="15" t="inlineStr">
+        <is>
+          <t>Emission Factor Validation</t>
+        </is>
+      </c>
+      <c r="C158" s="15" t="inlineStr">
+        <is>
+          <t>Argon EF matches current year standard</t>
+        </is>
+      </c>
+      <c r="D158" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E158" s="15" t="inlineStr">
+        <is>
+          <t>Lookup / reference</t>
+        </is>
+      </c>
+      <c r="F158" s="15" t="inlineStr">
+        <is>
+          <t>EF = lookup(input='argon', year=current)</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="42" customHeight="1">
+      <c r="A159" s="15" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B159" s="15" t="inlineStr">
+        <is>
+          <t>Emission Factor Validation</t>
+        </is>
+      </c>
+      <c r="C159" s="15" t="inlineStr">
+        <is>
+          <t>Electricity grid EF and REC generator EF match current year standard</t>
+        </is>
+      </c>
+      <c r="D159" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E159" s="15" t="inlineStr">
+        <is>
+          <t>Lookup / reference</t>
+        </is>
+      </c>
+      <c r="F159" s="15" t="inlineStr">
+        <is>
+          <t>EF = lookup(grid, year=current); REC_EF = lookup(generator, year=current)</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="42" customHeight="1">
+      <c r="A160" s="15" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B160" s="15" t="inlineStr">
+        <is>
+          <t>Emission Factor Validation</t>
+        </is>
+      </c>
+      <c r="C160" s="15" t="inlineStr">
+        <is>
+          <t>Brine process and embodied EFs match current year standard</t>
+        </is>
+      </c>
+      <c r="D160" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E160" s="15" t="inlineStr">
+        <is>
+          <t>Lookup / reference</t>
+        </is>
+      </c>
+      <c r="F160" s="15" t="inlineStr">
+        <is>
+          <t>EF = lookup(fluid='brine', component, year=current)</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="42" customHeight="1">
+      <c r="A161" s="15" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B161" s="15" t="inlineStr">
+        <is>
+          <t>Emission Factor Validation</t>
+        </is>
+      </c>
+      <c r="C161" s="15" t="inlineStr">
+        <is>
+          <t>Support travel EFs match current year standard (SAF, gasoline per mode)</t>
+        </is>
+      </c>
+      <c r="D161" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E161" s="15" t="inlineStr">
+        <is>
+          <t>Lookup / reference</t>
+        </is>
+      </c>
+      <c r="F161" s="15" t="inlineStr">
+        <is>
+          <t>EF = lookup(mode, year=current) for each travel mode</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="42" customHeight="1">
+      <c r="A162" s="15" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B162" s="15" t="inlineStr">
+        <is>
+          <t>Emission Factor Validation</t>
+        </is>
+      </c>
+      <c r="C162" s="15" t="inlineStr">
+        <is>
+          <t>Waste disposal EFs match current year standard (per disposal method)</t>
+        </is>
+      </c>
+      <c r="D162" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E162" s="15" t="inlineStr">
+        <is>
+          <t>Lookup / reference</t>
+        </is>
+      </c>
+      <c r="F162" s="15" t="inlineStr">
+        <is>
+          <t>EF = lookup(disposal_method, year=current)</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="42" customHeight="1">
+      <c r="A163" s="15" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B163" s="15" t="inlineStr">
+        <is>
+          <t>Emission Factor Validation</t>
+        </is>
+      </c>
+      <c r="C163" s="15" t="inlineStr">
+        <is>
+          <t>Railcar transport EFs match current year standard</t>
+        </is>
+      </c>
+      <c r="D163" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E163" s="15" t="inlineStr">
+        <is>
+          <t>Lookup / reference</t>
+        </is>
+      </c>
+      <c r="F163" s="15" t="inlineStr">
+        <is>
+          <t>EF = lookup(mode='railcar', year=current)</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="42" customHeight="1">
+      <c r="A164" s="15" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B164" s="15" t="inlineStr">
+        <is>
+          <t>Emission Factor Validation</t>
+        </is>
+      </c>
+      <c r="C164" s="15" t="inlineStr">
+        <is>
+          <t>All other category-specific EFs validated against standard list</t>
+        </is>
+      </c>
+      <c r="D164" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E164" s="15" t="inlineStr">
+        <is>
+          <t>Lookup / reference</t>
+        </is>
+      </c>
+      <c r="F164" s="15" t="inlineStr">
+        <is>
+          <t>Catch-all: any EF not covered above must match standard list</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="16" customHeight="1">
+      <c r="A165" s="12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B165" s="12" t="inlineStr">
+        <is>
+          <t>Multi-Scapegoat Allocation</t>
+        </is>
+      </c>
+      <c r="C165" s="12" t="n"/>
+      <c r="D165" s="12" t="n"/>
+      <c r="E165" s="12" t="n"/>
+      <c r="F165" s="12" t="n"/>
+    </row>
+    <row r="166" ht="42" customHeight="1">
+      <c r="A166" s="15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B166" s="15" t="inlineStr">
+        <is>
+          <t>Multi-Scapegoat Allocation</t>
+        </is>
+      </c>
+      <c r="C166" s="15" t="inlineStr">
+        <is>
+          <t>Total site emissions across all scapegoats equals evidence total</t>
+        </is>
+      </c>
+      <c r="D166" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E166" s="15" t="inlineStr">
+        <is>
+          <t>Arithmetic</t>
+        </is>
+      </c>
+      <c r="F166" s="15" t="inlineStr">
+        <is>
+          <t>Σ(scapegoat_emissions_i) = total_site_emissions; fail on non-zero residual</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="42" customHeight="1">
+      <c r="A167" s="15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B167" s="15" t="inlineStr">
+        <is>
+          <t>Multi-Scapegoat Allocation</t>
+        </is>
+      </c>
+      <c r="C167" s="15" t="inlineStr">
+        <is>
+          <t>No individual removal is net-emissive (seq − activities + reductions &gt; 0)</t>
+        </is>
+      </c>
+      <c r="D167" s="15" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E167" s="15" t="inlineStr">
+        <is>
+          <t>Threshold check</t>
+        </is>
+      </c>
+      <c r="F167" s="15" t="inlineStr">
+        <is>
+          <t>∀ removal: net_removal &gt; 0; net-emissive result = fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="42" customHeight="1">
+      <c r="A168" s="13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B168" s="13" t="inlineStr">
+        <is>
+          <t>Multi-Scapegoat Allocation</t>
+        </is>
+      </c>
+      <c r="C168" s="13" t="inlineStr">
+        <is>
+          <t>Allocation logic is reasonable and documented</t>
+        </is>
+      </c>
+      <c r="D168" s="13" t="inlineStr">
+        <is>
+          <t>Charm Review</t>
+        </is>
+      </c>
+      <c r="E168" s="13" t="inlineStr">
+        <is>
+          <t>Judgment call</t>
+        </is>
+      </c>
+      <c r="F168" s="13" t="inlineStr">
+        <is>
+          <t>Requires reading allocation documentation; reasonableness is qualitative</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>